--- a/NAMA NOP PANGKALANBUN.xlsx
+++ b/NAMA NOP PANGKALANBUN.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$45</definedName>
   </definedNames>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="56">
   <si>
     <t>NAMA</t>
   </si>
@@ -38,6 +41,12 @@
     <t>NOP</t>
   </si>
   <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longtitude</t>
+  </si>
+  <si>
     <t>AGUS SUGANDA</t>
   </si>
   <si>
@@ -125,7 +134,7 @@
     <t>HERMANSYAH</t>
   </si>
   <si>
-    <t>M. RIZKY</t>
+    <t>MUHAMMAD RIZKY</t>
   </si>
   <si>
     <t>RIDWANSYAH</t>
@@ -168,6 +177,30 @@
   </si>
   <si>
     <t>ARIF JONIAWAN</t>
+  </si>
+  <si>
+    <t>FIRDAUS</t>
+  </si>
+  <si>
+    <t>-2.51152</t>
+  </si>
+  <si>
+    <t>112.93989</t>
+  </si>
+  <si>
+    <t>AYU NUR ISLAMIAH</t>
+  </si>
+  <si>
+    <t>RAHMAT RIYAN WAHYUDIN</t>
+  </si>
+  <si>
+    <t>RONI YUDI ISYANTO</t>
+  </si>
+  <si>
+    <t>FHANNY AGUSTIAWAN</t>
+  </si>
+  <si>
+    <t>SUWITO</t>
   </si>
 </sst>
 </file>
@@ -180,7 +213,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,6 +227,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <charset val="134"/>
+      <scheme val="major"/>
     </font>
     <font>
       <u/>
@@ -340,7 +380,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,6 +391,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -681,55 +727,52 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -744,74 +787,77 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -821,7 +867,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1097,6 +1153,753 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="FME"/>
+      <sheetName val="Productivity Sep"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>RIZAL IHZAMAHENDRA</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>CME</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>-2.5388</v>
+          </cell>
+          <cell r="F2" t="str">
+            <v>112.8923</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>HAFID BUDIANTO</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>CME</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>-1.488357</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>110.567107</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>JOENDRIS HERDIAN KARA</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>CME</v>
+          </cell>
+          <cell r="E4" t="str">
+            <v>-2.70034</v>
+          </cell>
+          <cell r="F4" t="str">
+            <v>111.6329</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>DIAN WILDANI</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>-2.521661</v>
+          </cell>
+          <cell r="F5" t="str">
+            <v>110.209177</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>AGUS SUGANDA</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E6" t="str">
+            <v>-1.870035</v>
+          </cell>
+          <cell r="F6" t="str">
+            <v>109.969371</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>AJI SAPUTRA</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E7" t="str">
+            <v>-1.102318</v>
+          </cell>
+          <cell r="F7" t="str">
+            <v>109.961244</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>DANDI PUTRA</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E8" t="str">
+            <v>-1.85291</v>
+          </cell>
+          <cell r="F8" t="str">
+            <v>109.958184</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>DIAN WAHYUDI</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E9" t="str">
+            <v>-1.25064</v>
+          </cell>
+          <cell r="F9" t="str">
+            <v>110.51905</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>HERWANI</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E10" t="str">
+            <v>-1.246109</v>
+          </cell>
+          <cell r="F10" t="str">
+            <v>110.521564</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>IWAN ZAINAL ABIDIN</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E11" t="str">
+            <v>-1.826717</v>
+          </cell>
+          <cell r="F11" t="str">
+            <v>110.61551</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>PARYADI KUSUMA</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E12" t="str">
+            <v>-2.316346</v>
+          </cell>
+          <cell r="F12" t="str">
+            <v>110.824226</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>PONIRAN</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E13" t="str">
+            <v>-2.45948</v>
+          </cell>
+          <cell r="F13" t="str">
+            <v>111.027334</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>CAVIN ANDREAN EKA PUTRA</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E14" t="str">
+            <v>-2.193976</v>
+          </cell>
+          <cell r="F14" t="str">
+            <v>111.4407631</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>DADANG WAHYU SYAHPUTRA</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E15" t="str">
+            <v>-2.4241526</v>
+          </cell>
+          <cell r="F15" t="str">
+            <v>111.1016752</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>STEVEN HERDIAN KARA</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E16" t="str">
+            <v>-2.70034</v>
+          </cell>
+          <cell r="F16" t="str">
+            <v>111.6329</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>YUDIONO</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D17" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E17" t="str">
+            <v>-2.517327</v>
+          </cell>
+          <cell r="F17" t="str">
+            <v>111.7697441</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>ARDI</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E18" t="str">
+            <v>-2.185169</v>
+          </cell>
+          <cell r="F18" t="str">
+            <v>111.452512</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>ANDARIANTO PUJI SURO</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D19" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E19" t="str">
+            <v>-3.3833150</v>
+          </cell>
+          <cell r="F19" t="str">
+            <v>112.5405820</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>FERI HARIADI</v>
+          </cell>
+          <cell r="C20" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E20" t="str">
+            <v>-2.463143</v>
+          </cell>
+          <cell r="F20" t="str">
+            <v>112.44791</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>NASUKI</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D21" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E21" t="str">
+            <v>-2.52924</v>
+          </cell>
+          <cell r="F21">
+            <v>112.94876</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>SOLEKHAN</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E22" t="str">
+            <v>-1.859777</v>
+          </cell>
+          <cell r="F22" t="str">
+            <v>112.664680</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>TEGUH WICAKSONO</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E23" t="str">
+            <v>-2.461650</v>
+          </cell>
+          <cell r="F23" t="str">
+            <v>112.447721</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>REDI CANDRA SINAGA</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D24" t="str">
+            <v>MBP</v>
+          </cell>
+          <cell r="E24" t="str">
+            <v>-2.022953</v>
+          </cell>
+          <cell r="F24" t="str">
+            <v>112.788943</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>IPAN HARIONO</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v>PM</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>-1.821824</v>
+          </cell>
+          <cell r="F25" t="str">
+            <v>109.959643</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>DIDIK PRIYONO</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D26" t="str">
+            <v>PM</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>-2.7118</v>
+          </cell>
+          <cell r="F26" t="str">
+            <v>111.6423</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>MUHAMAD ROIS FERDIANSYAH</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D27" t="str">
+            <v>PM</v>
+          </cell>
+          <cell r="E27" t="str">
+            <v>-2.51152</v>
+          </cell>
+          <cell r="F27" t="str">
+            <v>112.93989</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>WIDI ARYANTO</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v>PM</v>
+          </cell>
+          <cell r="E28" t="str">
+            <v>-2.51152</v>
+          </cell>
+          <cell r="F28" t="str">
+            <v>112.93989</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>RIDWANSYAH</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E29" t="str">
+            <v>-1.194989</v>
+          </cell>
+          <cell r="F29" t="str">
+            <v>110.008519</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>MUHAMMAD RIZKY</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D30" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E30" t="str">
+            <v>-1.827840</v>
+          </cell>
+          <cell r="F30" t="str">
+            <v>110.611589</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>TRIYONO</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D31" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E31" t="str">
+            <v>-2.29781</v>
+          </cell>
+          <cell r="F31" t="str">
+            <v>110.84351</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>UTI MUHAMMAD KHAIRUL HUDA</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D32" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E32" t="str">
+            <v>-1.849856</v>
+          </cell>
+          <cell r="F32" t="str">
+            <v>109.979862</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>HERMANSYAH</v>
+          </cell>
+          <cell r="C33" t="str">
+            <v>KETAPANG</v>
+          </cell>
+          <cell r="D33" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E33" t="str">
+            <v>-1.472642</v>
+          </cell>
+          <cell r="F33" t="str">
+            <v>110.559704</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>BAGUS SANTOSO</v>
+          </cell>
+          <cell r="C34" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D34" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E34" t="str">
+            <v>-2.722527</v>
+          </cell>
+          <cell r="F34" t="str">
+            <v>111.583390</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>M.ABDUL KHOLIP</v>
+          </cell>
+          <cell r="C35" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D35" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E35" t="str">
+            <v>-2.6689</v>
+          </cell>
+          <cell r="F35" t="str">
+            <v>111.65701</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>RIRIH HARIANTO</v>
+          </cell>
+          <cell r="C36" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D36" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E36" t="str">
+            <v>-2.708090</v>
+          </cell>
+          <cell r="F36" t="str">
+            <v>111.622607</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>BONDAN PRAMUDYA ANANTATUR</v>
+          </cell>
+          <cell r="C37" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D37" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E37" t="str">
+            <v>-2.03423</v>
+          </cell>
+          <cell r="F37" t="str">
+            <v>112.79966</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>ARDIANSYAH</v>
+          </cell>
+          <cell r="C38" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D38" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E38" t="str">
+            <v>-1.861329</v>
+          </cell>
+          <cell r="F38" t="str">
+            <v>112.659606</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39" t="str">
+            <v>MUJHAHID ALWI</v>
+          </cell>
+          <cell r="C39" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D39" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E39" t="str">
+            <v>-2.51152</v>
+          </cell>
+          <cell r="F39" t="str">
+            <v>112.93989</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>TAJAM SAPUTRA</v>
+          </cell>
+          <cell r="C40" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D40" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E40" t="str">
+            <v>-2.519362</v>
+          </cell>
+          <cell r="F40" t="str">
+            <v>112.473034</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41" t="str">
+            <v>WAHYUDI</v>
+          </cell>
+          <cell r="C41" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D41" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E41" t="str">
+            <v>-2.52959</v>
+          </cell>
+          <cell r="F41" t="str">
+            <v>112.94859</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42" t="str">
+            <v>Mei Nugroho Dwi Laksono</v>
+          </cell>
+          <cell r="C42" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D42" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E42" t="str">
+            <v>-2.185169</v>
+          </cell>
+          <cell r="F42" t="str">
+            <v>111.452512</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43" t="str">
+            <v>Arif Joniawan</v>
+          </cell>
+          <cell r="C43" t="str">
+            <v>PANGKALANBUN</v>
+          </cell>
+          <cell r="D43" t="str">
+            <v>TE</v>
+          </cell>
+          <cell r="E43" t="str">
+            <v>-2.663056</v>
+          </cell>
+          <cell r="F43" t="str">
+            <v>111.260303</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44" t="str">
+            <v>DAYU SHANDY</v>
+          </cell>
+          <cell r="C44" t="str">
+            <v>SAMPIT</v>
+          </cell>
+          <cell r="D44" t="str">
+            <v>TF</v>
+          </cell>
+          <cell r="E44" t="str">
+            <v>-1.8605120</v>
+          </cell>
+          <cell r="F44" t="str">
+            <v>112.6649540</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1347,540 +2150,950 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B88"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="1"/>
+  <dimension ref="A1:D88"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="30.2727272727273" customWidth="1"/>
     <col min="2" max="2" width="21.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="7" t="str">
+        <f>VLOOKUP(A2,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.870035</v>
+      </c>
+      <c r="D2" s="7" t="str">
+        <f>VLOOKUP(A2,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>109.969371</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="7" t="str">
+        <f>VLOOKUP(A3,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.102318</v>
+      </c>
+      <c r="D3" s="7" t="str">
+        <f>VLOOKUP(A3,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>109.961244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="7" t="str">
+        <f>VLOOKUP(A4,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.85291</v>
+      </c>
+      <c r="D4" s="7" t="str">
+        <f>VLOOKUP(A4,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>109.958184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="7" t="str">
+        <f>VLOOKUP(A5,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.25064</v>
+      </c>
+      <c r="D5" s="7" t="str">
+        <f>VLOOKUP(A5,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>110.51905</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="7" t="str">
+        <f>VLOOKUP(A6,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.521661</v>
+      </c>
+      <c r="D6" s="7" t="str">
+        <f>VLOOKUP(A6,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>110.209177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="7" t="str">
+        <f>VLOOKUP(A7,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.488357</v>
+      </c>
+      <c r="D7" s="7" t="str">
+        <f>VLOOKUP(A7,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>110.567107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="str">
+        <f>VLOOKUP(A8,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.246109</v>
+      </c>
+      <c r="D8" s="7" t="str">
+        <f>VLOOKUP(A8,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>110.521564</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="7" t="str">
+        <f>VLOOKUP(A9,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.826717</v>
+      </c>
+      <c r="D9" s="7" t="str">
+        <f>VLOOKUP(A9,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>110.61551</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>13</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="7" t="str">
+        <f>VLOOKUP(A10,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.316346</v>
+      </c>
+      <c r="D10" s="7" t="str">
+        <f>VLOOKUP(A10,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>110.824226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>14</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="7" t="str">
+        <f>VLOOKUP(A11,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.45948</v>
+      </c>
+      <c r="D11" s="7" t="str">
+        <f>VLOOKUP(A11,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.027334</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>15</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="7" t="str">
+        <f>VLOOKUP(A12,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-3.3833150</v>
+      </c>
+      <c r="D12" s="7" t="str">
+        <f>VLOOKUP(A12,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.5405820</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>16</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="7" t="str">
+        <f>VLOOKUP(A13,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.185169</v>
+      </c>
+      <c r="D13" s="7" t="str">
+        <f>VLOOKUP(A13,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.452512</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>17</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="7" t="str">
+        <f>VLOOKUP(A14,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.193976</v>
+      </c>
+      <c r="D14" s="7" t="str">
+        <f>VLOOKUP(A14,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.4407631</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>18</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="7" t="str">
+        <f>VLOOKUP(A15,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.4241526</v>
+      </c>
+      <c r="D15" s="7" t="str">
+        <f>VLOOKUP(A15,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.1016752</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>19</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="7" t="str">
+        <f>VLOOKUP(A16,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.463143</v>
+      </c>
+      <c r="D16" s="7" t="str">
+        <f>VLOOKUP(A16,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.44791</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>20</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="7" t="str">
+        <f>VLOOKUP(A17,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.70034</v>
+      </c>
+      <c r="D17" s="7" t="str">
+        <f>VLOOKUP(A17,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.6329</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>21</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="7" t="str">
+        <f>VLOOKUP(A18,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.52924</v>
+      </c>
+      <c r="D18">
+        <f>VLOOKUP(A18,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.94876</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>22</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="7" t="str">
+        <f>VLOOKUP(A19,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.022953</v>
+      </c>
+      <c r="D19" s="7" t="str">
+        <f>VLOOKUP(A19,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.788943</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>23</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="7" t="str">
+        <f>VLOOKUP(A20,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.5388</v>
+      </c>
+      <c r="D20" s="7" t="str">
+        <f>VLOOKUP(A20,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.8923</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>24</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="7" t="str">
+        <f>VLOOKUP(A21,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.859777</v>
+      </c>
+      <c r="D21" s="7" t="str">
+        <f>VLOOKUP(A21,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.664680</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>25</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="7" t="str">
+        <f>VLOOKUP(A22,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.70034</v>
+      </c>
+      <c r="D22" s="7" t="str">
+        <f>VLOOKUP(A22,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.6329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>26</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="7" t="str">
+        <f>VLOOKUP(A23,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.461650</v>
+      </c>
+      <c r="D23" s="7" t="str">
+        <f>VLOOKUP(A23,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.447721</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>27</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="7" t="str">
+        <f>VLOOKUP(A24,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.517327</v>
+      </c>
+      <c r="D24" s="7" t="str">
+        <f>VLOOKUP(A24,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.7697441</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>28</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="7" t="str">
+        <f>VLOOKUP(A25,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.821824</v>
+      </c>
+      <c r="D25" s="7" t="str">
+        <f>VLOOKUP(A25,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>109.959643</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>29</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="7" t="str">
+        <f>VLOOKUP(A26,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.7118</v>
+      </c>
+      <c r="D26" s="7" t="str">
+        <f>VLOOKUP(A26,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.6423</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>30</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="7" t="str">
+        <f>VLOOKUP(A27,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.51152</v>
+      </c>
+      <c r="D27" s="7" t="str">
+        <f>VLOOKUP(A27,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.93989</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>31</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="7" t="str">
+        <f>VLOOKUP(A28,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.51152</v>
+      </c>
+      <c r="D28" s="7" t="str">
+        <f>VLOOKUP(A28,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.93989</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>32</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="7" t="str">
+        <f>VLOOKUP(A29,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.472642</v>
+      </c>
+      <c r="D29" s="7" t="str">
+        <f>VLOOKUP(A29,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>110.559704</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="7" t="str">
+        <f>VLOOKUP(A30,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.827840</v>
+      </c>
+      <c r="D30" s="7" t="str">
+        <f>VLOOKUP(A30,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>110.611589</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>34</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="7" t="str">
+        <f>VLOOKUP(A31,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.194989</v>
+      </c>
+      <c r="D31" s="7" t="str">
+        <f>VLOOKUP(A31,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>110.008519</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>35</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="7" t="str">
+        <f>VLOOKUP(A32,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.29781</v>
+      </c>
+      <c r="D32" s="7" t="str">
+        <f>VLOOKUP(A32,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>110.84351</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>36</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="7" t="str">
+        <f>VLOOKUP(A33,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.849856</v>
+      </c>
+      <c r="D33" s="7" t="str">
+        <f>VLOOKUP(A33,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>109.979862</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>37</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="7" t="str">
+        <f>VLOOKUP(A34,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.861329</v>
+      </c>
+      <c r="D34" s="7" t="str">
+        <f>VLOOKUP(A34,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.659606</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>38</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="7" t="str">
+        <f>VLOOKUP(A35,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.722527</v>
+      </c>
+      <c r="D35" s="7" t="str">
+        <f>VLOOKUP(A35,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.583390</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>39</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="7" t="str">
+        <f>VLOOKUP(A36,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.03423</v>
+      </c>
+      <c r="D36" s="7" t="str">
+        <f>VLOOKUP(A36,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.79966</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>40</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="7" t="str">
+        <f>VLOOKUP(A37,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.6689</v>
+      </c>
+      <c r="D37" s="7" t="str">
+        <f>VLOOKUP(A37,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.65701</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>41</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="7" t="str">
+        <f>VLOOKUP(A38,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.51152</v>
+      </c>
+      <c r="D38" s="7" t="str">
+        <f>VLOOKUP(A38,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.93989</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>42</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="7" t="str">
+        <f>VLOOKUP(A39,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.708090</v>
+      </c>
+      <c r="D39" s="7" t="str">
+        <f>VLOOKUP(A39,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.622607</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>43</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="7" t="str">
+        <f>VLOOKUP(A40,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.519362</v>
+      </c>
+      <c r="D40" s="7" t="str">
+        <f>VLOOKUP(A40,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.473034</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>44</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="7" t="str">
+        <f>VLOOKUP(A41,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.52959</v>
+      </c>
+      <c r="D41" s="7" t="str">
+        <f>VLOOKUP(A41,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.94859</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>45</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="7" t="str">
+        <f>VLOOKUP(A42,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-1.8605120</v>
+      </c>
+      <c r="D42" s="7" t="str">
+        <f>VLOOKUP(A42,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>112.6649540</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>46</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="7" t="str">
+        <f>VLOOKUP(A43,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.185169</v>
+      </c>
+      <c r="D43" s="7" t="str">
+        <f>VLOOKUP(A43,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.452512</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="7" t="str">
+        <f>VLOOKUP(A44,[1]FME!$B$2:$E$44,4,FALSE)</f>
+        <v>-2.663056</v>
+      </c>
+      <c r="D44" s="7" t="str">
+        <f>VLOOKUP(A44,[1]FME!$B$2:$F$44,5,FALSE)</f>
+        <v>111.260303</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B45" etc:filterBottomFollowUsedRange="0">

--- a/NAMA NOP PANGKALANBUN.xlsx
+++ b/NAMA NOP PANGKALANBUN.xlsx
@@ -41,10 +41,10 @@
     <t>NOP</t>
   </si>
   <si>
-    <t>Latitude</t>
-  </si>
-  <si>
-    <t>Longtitude</t>
+    <t>Latitude Berangkat</t>
+  </si>
+  <si>
+    <t>Longtitude Berangkat</t>
   </si>
   <si>
     <t>AGUS SUGANDA</t>
